--- a/1. RAG/data/4_testing/range_of_k/RAG_eval_k=10.xlsx
+++ b/1. RAG/data/4_testing/range_of_k/RAG_eval_k=10.xlsx
@@ -548,35 +548,35 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>I don't have enough information to answer that.</t>
+          <t>According to the data provided, 2% of gay men in Germany reported feeling discriminated against in the past year when showing their ID or any official document that identifies their sex.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7144</v>
+        <v>0.7181</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.63</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>61.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="3">
@@ -590,35 +590,35 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Lesbian women in France feel the following about being open about their identity at work: 18% are always open, 54% are selectively open, and 28% hide their LGBT identity.</t>
+          <t>According to the provided responses from the context, 18% of lesbian women in France are always open about their identity at work, 54% are selectively open, and 28% hide their LGBT identity. This suggests that while there is a significant portion of lesbian women who feel comfortable being open, a majority are either selectively open or choose to hide their identity.</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.6838</v>
+        <v>0.6972</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="I3" s="4" t="b">
         <v>1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.6</v>
+        <v>0.293</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>31.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="4">
@@ -639,13 +639,13 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7042</v>
+        <v>0.6657</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>8</v>
@@ -681,13 +681,13 @@
         <v>10</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.6616</v>
+        <v>0.6629</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>8</v>
@@ -729,7 +729,7 @@
         <v>0.8</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5737</v>
+        <v>0.5775</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>8</v>
@@ -765,13 +765,13 @@
         <v>10</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5495</v>
+        <v>0.5597</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>8</v>
@@ -807,13 +807,13 @@
         <v>10</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5132</v>
+        <v>0.51</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>8</v>
@@ -852,10 +852,10 @@
         <v>2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6081</v>
+        <v>0.3295</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>8</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0.182</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_b_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E2" s="2" t="b">
@@ -949,7 +949,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_b — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Gay? | Germany responses (Transgender): Yes: 39%, No: 55%, Don`t know: 6%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,13 @@
       <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -991,17 +987,13 @@
       <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1009,17 @@
       <c r="C5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1039,13 +1035,17 @@
       <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1061,13 +1061,17 @@
       <c r="C7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1089,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E8" s="2" t="b">
@@ -1093,7 +1097,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1115,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E9" s="4" t="b">
@@ -1119,7 +1123,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E10" s="2" t="b">
@@ -1145,7 +1149,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1167,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E11" s="4" t="b">
@@ -1171,7 +1175,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1364,14 +1368,18 @@
       <c r="C19" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
+        </is>
+      </c>
       <c r="E19" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in France: Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
-Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in Germany: Always open: 12%, selectively open: 62%, hide LGBT identity: 26%</t>
+          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Gay): Always open: 22%, selectively open: 49%, hide LGBT identity: 30%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Lesbian): Always open: 18%, selectively open: 54%, hide LGBT identity: 28%</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1397,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\open_at_work_answer_by_Bisexualwomen.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
         </is>
       </c>
       <c r="E20" s="2" t="b">
@@ -1397,8 +1405,8 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in France: Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
-Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in Germany: Always open: 12%, selectively open: 62%, hide LGBT identity: 26%</t>
+          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Gay): Always open: 22%, selectively open: 49%, hide LGBT identity: 30%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Lesbian): Always open: 18%, selectively open: 54%, hide LGBT identity: 28%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1424,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\open_at_work_answer_by_Bisexualwomen.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
         </is>
       </c>
       <c r="E21" s="4" t="b">
@@ -1424,8 +1432,8 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in France: Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
-Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in Germany: Always open: 12%, selectively open: 62%, hide LGBT identity: 26%</t>
+          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Gay): Always open: 22%, selectively open: 49%, hide LGBT identity: 30%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Lesbian): Always open: 18%, selectively open: 54%, hide LGBT identity: 28%</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1455,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1477,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1485,13 +1493,17 @@
       <c r="C24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1521,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E25" s="4" t="b">
@@ -1517,7 +1529,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1547,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E26" s="2" t="b">
@@ -1543,7 +1555,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1573,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E27" s="4" t="b">
@@ -1569,7 +1581,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1599,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E28" s="2" t="b">
@@ -1595,7 +1607,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1611,13 +1623,17 @@
       <c r="C29" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1633,13 +1649,17 @@
       <c r="C30" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1677,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b1_c_answer_by_Transgender.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E31" s="4" t="b">
@@ -1665,7 +1685,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1853,15 +1873,15 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b2_i_answer_by_Sweden.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b2_i_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E39" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Sweden responses (Gay): Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
+          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Gay responses in Sweden: Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
         </is>
       </c>
     </row>
@@ -1877,13 +1897,17 @@
       <c r="C40" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b2_i_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Sweden responses (Gay): Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
+          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Gay responses in Sweden: Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1925,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b2_i_answer_by_Sweden.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b2_i_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E41" s="4" t="b">
@@ -1909,7 +1933,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Sweden responses (Gay): Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
+          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Gay responses in Sweden: Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
         </is>
       </c>
     </row>
@@ -1925,24 +1949,22 @@
       <c r="C42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1958,24 +1980,22 @@
       <c r="C43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="5" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E43" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1991,28 +2011,18 @@
       <c r="C44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2028,28 +2038,18 @@
       <c r="C45" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D45" s="5" t="inlineStr"/>
       <c r="E45" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2065,28 +2065,18 @@
       <c r="C46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2102,24 +2092,22 @@
       <c r="C47" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D47" s="5" t="inlineStr"/>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E47" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2135,24 +2123,22 @@
       <c r="C48" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2168,24 +2154,22 @@
       <c r="C49" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D49" s="5" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E49" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2187,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E50" s="2" t="b">
@@ -2211,18 +2195,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2240,26 +2218,15 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E51" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Estimated ART coverage among people living with HIV (%)_max in Luxembourg: 86.0</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2242,11 @@
       <c r="C52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="b">
         <v>0</v>
       </c>
@@ -2331,11 +2302,7 @@
       <c r="C54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
-        </is>
-      </c>
+      <c r="D54" s="3" t="inlineStr"/>
       <c r="E54" s="2" t="b">
         <v>1</v>
       </c>
@@ -2427,7 +2394,11 @@
       <c r="C57" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D57" s="5" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E57" s="4" t="b">
         <v>1</v>
       </c>
@@ -2487,19 +2458,23 @@
       <c r="C59" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D59" s="5" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E59" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Reported number of people receiving ART in Slovakia: 650
-Estimated number of people living with HIV_median in Slovakia: 1200.0
-Estimated number of people living with HIV_min in Slovakia: 910.0
-Estimated number of people living with HIV_max in Slovakia: 1900.0
-Estimated ART coverage among people living with HIV (%)_median in Slovakia: 54.0
-Estimated ART coverage among people living with HIV (%)_min in Slovakia: 40.0
-Estimated ART coverage among people living with HIV (%)_max in Slovakia: 85.0</t>
+          <t>Reported number of people receiving ART in Croatia: 1200
+Estimated number of people living with HIV_median in Croatia: 1600.0
+Estimated number of people living with HIV_min in Croatia: 1400.0
+Estimated number of people living with HIV_max in Croatia: 1700.0
+Estimated ART coverage among people living with HIV (%)_median in Croatia: 75.0
+Estimated ART coverage among people living with HIV (%)_min in Croatia: 67.0
+Estimated ART coverage among people living with HIV (%)_max in Croatia: 83.0</t>
         </is>
       </c>
     </row>
@@ -2515,19 +2490,23 @@
       <c r="C60" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Reported number of people receiving ART in Slovakia: 650
-Estimated number of people living with HIV_median in Slovakia: 1200.0
-Estimated number of people living with HIV_min in Slovakia: 910.0
-Estimated number of people living with HIV_max in Slovakia: 1900.0
-Estimated ART coverage among people living with HIV (%)_median in Slovakia: 54.0
-Estimated ART coverage among people living with HIV (%)_min in Slovakia: 40.0
-Estimated ART coverage among people living with HIV (%)_max in Slovakia: 85.0</t>
+          <t>Reported number of people receiving ART in Croatia: 1200
+Estimated number of people living with HIV_median in Croatia: 1600.0
+Estimated number of people living with HIV_min in Croatia: 1400.0
+Estimated number of people living with HIV_max in Croatia: 1700.0
+Estimated ART coverage among people living with HIV (%)_median in Croatia: 75.0
+Estimated ART coverage among people living with HIV (%)_min in Croatia: 67.0
+Estimated ART coverage among people living with HIV (%)_max in Croatia: 83.0</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2524,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Slovakia.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
         </is>
       </c>
       <c r="E61" s="4" t="b">
@@ -2553,13 +2532,13 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Reported number of people receiving ART in Slovakia: 650
-Estimated number of people living with HIV_median in Slovakia: 1200.0
-Estimated number of people living with HIV_min in Slovakia: 910.0
-Estimated number of people living with HIV_max in Slovakia: 1900.0
-Estimated ART coverage among people living with HIV (%)_median in Slovakia: 54.0
-Estimated ART coverage among people living with HIV (%)_min in Slovakia: 40.0
-Estimated ART coverage among people living with HIV (%)_max in Slovakia: 85.0</t>
+          <t>Reported number of people receiving ART in Croatia: 1200
+Estimated number of people living with HIV_median in Croatia: 1600.0
+Estimated number of people living with HIV_min in Croatia: 1400.0
+Estimated number of people living with HIV_max in Croatia: 1700.0
+Estimated ART coverage among people living with HIV (%)_median in Croatia: 75.0
+Estimated ART coverage among people living with HIV (%)_min in Croatia: 67.0
+Estimated ART coverage among people living with HIV (%)_max in Croatia: 83.0</t>
         </is>
       </c>
     </row>
@@ -2575,25 +2554,28 @@
       <c r="C62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2609,25 +2591,28 @@
       <c r="C63" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D63" s="5" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E63" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2643,29 +2628,24 @@
       <c r="C64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D64" s="3" t="inlineStr"/>
       <c r="E64" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2681,29 +2661,24 @@
       <c r="C65" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D65" s="5" t="inlineStr"/>
       <c r="E65" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2719,29 +2694,24 @@
       <c r="C66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2729,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E67" s="4" t="b">
@@ -2767,19 +2737,18 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2795,21 +2764,28 @@
       <c r="C68" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2803,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E69" s="4" t="b">
@@ -2835,15 +2811,18 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2840,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E70" s="2" t="b">
@@ -2869,15 +2848,18 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2877,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E71" s="4" t="b">
@@ -2903,15 +2885,18 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2933,19 +2918,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2961,29 +2934,13 @@
       <c r="C73" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
-        </is>
-      </c>
+      <c r="D73" s="5" t="inlineStr"/>
       <c r="E73" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -3001,7 +2958,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E74" s="2" t="b">
@@ -3009,19 +2966,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -3039,7 +2984,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E75" s="4" t="b">
@@ -3047,19 +2992,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3010,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E76" s="2" t="b">
@@ -3085,19 +3018,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -3115,26 +3036,15 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E77" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -3150,24 +3060,17 @@
       <c r="C78" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3088,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E79" s="4" t="b">
@@ -3193,18 +3096,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3114,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E80" s="2" t="b">
@@ -3230,18 +3122,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3140,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E81" s="4" t="b">
@@ -3267,18 +3148,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
